--- a/INMUEBLES_15.xlsx
+++ b/INMUEBLES_15.xlsx
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KEVIN2\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://itculiacanedu-my.sharepoint.com/personal/16170745_itculiacan_edu_mx/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{538BA336-85F0-4B00-82C4-B223AA317CA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EED04A57-B04B-42B1-B654-AC5658ADD432}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3675" yWindow="3675" windowWidth="17325" windowHeight="10830" xr2:uid="{B4CDD858-46A5-4189-9ECA-38502CC0098C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B4CDD858-46A5-4189-9ECA-38502CC0098C}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$E$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$E$8</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="31">
   <si>
     <t>No.</t>
   </si>
@@ -48,45 +48,12 @@
     <t>CALLE DEL PASTIZAL</t>
   </si>
   <si>
-    <t>CIRCUITO VALLE DE LOS ENCINOS</t>
-  </si>
-  <si>
-    <t>*COBACHBC PLANTEL EXTENSIÓN LA PRESA (90 M)
-*ESTACION DE BOMBEROS PARAJES DEL VALLE (160 M)
-*ESCUELA PRIMARIA VICENTE SUÁREZ (385 M)
-*JARDIN DE NIÑOS XOCHIPILLI (430 M)</t>
-  </si>
-  <si>
     <t>MARGARITA RESIDENCIAL/PRESA ESTE</t>
   </si>
   <si>
-    <t>PARAJES DEL VALLE/PRESA ESTE</t>
-  </si>
-  <si>
-    <t>HACIENDA LAS DELICIAS/PRESA ESTE</t>
-  </si>
-  <si>
-    <t>PARQUE INDUSTRIAL PACIFICO 4TA ETAPA/SANCHEZ TABOADA</t>
-  </si>
-  <si>
-    <t>EL LAUREL/PRESA ESTE</t>
-  </si>
-  <si>
-    <t>PARQUE INDUSTRIAL VALLE DEL SUR II/SAN ANTONIO DE LOS BUENOS</t>
-  </si>
-  <si>
-    <t>PASEOS DEL VERGEL/PRESA ESTE</t>
-  </si>
-  <si>
-    <t>GRANJAS ECUESTRES/PLAYAS DE TIJUANA</t>
-  </si>
-  <si>
     <t>PASEOS DEL FLORIDO CALIFORNIA/PRESA ESTE</t>
   </si>
   <si>
-    <t>RIBERA DEL BOSQUE/OTAY CENTENARIO</t>
-  </si>
-  <si>
     <t>LOMAS DE SANTA FE/PLAYAS DE TIJUANA</t>
   </si>
   <si>
@@ -97,26 +64,6 @@
   </si>
   <si>
     <t>FRANCISCO ZARCO/SAN ANTONIO DE LOS BUENOS</t>
-  </si>
-  <si>
-    <t>CALLE ARROYO DEL CAMPO</t>
-  </si>
-  <si>
-    <t>*IGLESIA PENTECOSTES EL BUEN PASTOR HACIENDA LAS DELICIAS 1 (35 M)
-*PARQUE DE DELICIAS (400 M)
-*CENTRO COMUNITARIO MUNICIPAL LAS DELICIAS (415 M)
-*ESTACIÓN DE BOMBEROS HACIENDA LAS DELICIAS (770 M)</t>
-  </si>
-  <si>
-    <t>ACAPULCO</t>
-  </si>
-  <si>
-    <t>DE LOS CARLOS</t>
-  </si>
-  <si>
-    <t>*TELESECUNDARIA No. 24 "PABLO CASAS" (985 M)
-*PRIMARIA GENARO VAZQUEZ (1.06 KM)
-*JARDIN DE NIÑOS CECILIA GRIERSON (640 M)</t>
   </si>
   <si>
     <t>*AZTEK WAR PAINTBALL PARK (1.5 KM)</t>
@@ -136,25 +83,11 @@
 *ESTACION DE BOMBEROS SANTA FÉ (855 M)</t>
   </si>
   <si>
-    <t>*PRIMARIA MAESTROS MEXICANOS (445 M)
-*JARDIN DE NUÑOS FERNANDO MONTES (475 M)
-*UNIDAD DE MEDICINA FAMLIAR NO. 18 (455 M)</t>
-  </si>
-  <si>
     <t>*PARQUE CLAVEL (60 M)
 *PARQUE LIRIOS (150 M)
 *ESCUELA SECUNDARIA NUEVA CREACION MARGARITA RESIDENCIAL (500 M)</t>
   </si>
   <si>
-    <t>CALLE TURQUEZA</t>
-  </si>
-  <si>
-    <t>*PARQUE ACACIAS (290 M)
-*PARQUE BANDFIELD (540 M)
-*IGLESIA MISERICORDIA DE DIOS (950 M)
-*CALIMAX RIBERAS DEL BOSQUE (720M)</t>
-  </si>
-  <si>
     <t>*PARQUE LOMAS SANTA FE II (250 M)
 *CASA CLUB VIÑAS DEL REAL (650M)
 *ECOPARQUE LAS CASCADAS (850M)</t>
@@ -172,60 +105,13 @@
     <t>CALLE REAL DEL MAR</t>
   </si>
   <si>
-    <t>PRIVADA SAN ANTONIO</t>
-  </si>
-  <si>
-    <t>AV.DE LOS NOGALES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BLVD. VIÑAS DEL MAR </t>
-  </si>
-  <si>
     <t>AV.PASEOS DEL FLORIDO</t>
   </si>
   <si>
-    <t>*PREPARATORIA FEDERAL LAZARO CARDENAS III VALLE SUR (570 M)
-*PARQUE EN COLONIA PARQUE INDUSTRIALL VALLE DEL SUR II(1 KM)</t>
-  </si>
-  <si>
-    <t>*ESCUELA SECUNDARIA TECNICA #51 (580 M)
-*JARDIN DE NIÑOS AZTECA (580 M)
-*ESCUELA PRIMARIA PAI PAI(450 M)
-*PARQUE PASEO DEL VERGEL(700 M)</t>
-  </si>
-  <si>
-    <t>*PARQUE VIÑAS DEL MAR III (750 M)
-*PARQUE LOMA SANTA FE II (910 M)</t>
-  </si>
-  <si>
     <t>BZ089004</t>
   </si>
   <si>
-    <t>VC107011</t>
-  </si>
-  <si>
-    <t>SU317004</t>
-  </si>
-  <si>
-    <t>PP401008</t>
-  </si>
-  <si>
-    <t>FD941015</t>
-  </si>
-  <si>
-    <t>XL323004</t>
-  </si>
-  <si>
-    <t>FD663016</t>
-  </si>
-  <si>
-    <t>KB257021</t>
-  </si>
-  <si>
     <t>FD536009</t>
-  </si>
-  <si>
-    <t>MZ792002</t>
   </si>
   <si>
     <t>KC049001</t>
@@ -255,9 +141,25 @@
   <numFmts count="1">
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00;[Red]\-&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -299,29 +201,43 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="8" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="8" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -341,9 +257,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -381,7 +297,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -487,7 +403,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -629,7 +545,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -637,289 +553,154 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68123CE7-9C62-46E6-88E6-0767FEB3B5BD}">
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="63.85546875" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="31.28515625" customWidth="1"/>
-    <col min="5" max="5" width="55.42578125" customWidth="1"/>
+    <col min="1" max="1" width="9" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="63" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.42578125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30.28515625" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="66.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:5" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="10" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="60" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
+    <row r="2" spans="1:5" s="9" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="12">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" s="9" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="12">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" s="9" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="12">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="C4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" s="9" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="12">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" s="9" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="12">
         <v>5</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>32</v>
+      <c r="B6" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="60" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D3" s="3" t="s">
+    <row r="7" spans="1:5" s="9" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="12">
         <v>6</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="B7" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" s="9" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="12">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" ht="75" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
+      <c r="B8" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="60" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="60" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <v>7</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>14</v>
-      </c>
       <c r="C8" s="1" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
-        <v>8</v>
-      </c>
-      <c r="B9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="5" t="s">
         <v>15</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="60" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
-        <v>9</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="60" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
-        <v>10</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
-        <v>11</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
-        <v>12</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
-        <v>13</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A15" s="1">
-        <v>14</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A16" s="1">
-        <v>15</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>30</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E16" xr:uid="{68123CE7-9C62-46E6-88E6-0767FEB3B5BD}"/>
+  <autoFilter ref="A1:E8" xr:uid="{68123CE7-9C62-46E6-88E6-0767FEB3B5BD}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>